--- a/backend/data/financials_by_company/0486.HK.xlsx
+++ b/backend/data/financials_by_company/0486.HK.xlsx
@@ -662,194 +662,202 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-41089743.589744</v>
+        <v>-12760000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06410299999999999</v>
+        <v>0.11</v>
       </c>
       <c r="D2" t="n">
-        <v>2425000000</v>
+        <v>4725000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-641000000</v>
+        <v>-116000000</v>
       </c>
       <c r="F2" t="n">
-        <v>-641000000</v>
+        <v>-116000000</v>
       </c>
       <c r="G2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
       <c r="H2" t="n">
-        <v>538000000</v>
+        <v>596000000</v>
       </c>
       <c r="I2" t="n">
-        <v>9261000000</v>
+        <v>8273000000</v>
       </c>
       <c r="J2" t="n">
-        <v>1784000000</v>
+        <v>4609000000</v>
       </c>
       <c r="K2" t="n">
-        <v>1246000000</v>
+        <v>4013000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-296000000</v>
+        <v>-329000000</v>
       </c>
       <c r="M2" t="n">
-        <v>388000000</v>
+        <v>372000000</v>
       </c>
       <c r="N2" t="n">
-        <v>121000000</v>
+        <v>43000000</v>
       </c>
       <c r="O2" t="n">
-        <v>1402910256.410256</v>
+        <v>3328240000</v>
       </c>
       <c r="P2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>11134000000</v>
+        <v>9706000000</v>
       </c>
       <c r="R2" t="n">
-        <v>368000000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>2079000000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15193014862</v>
+      </c>
+      <c r="T2" t="n">
+        <v>15193014862</v>
+      </c>
       <c r="U2" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>0.212</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.212</v>
+      </c>
       <c r="W2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
       <c r="X2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>55000000</v>
+        <v>416000000</v>
       </c>
       <c r="AD2" t="n">
-        <v>858000000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>3641000000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-60000000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-580000000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>283000000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-492000000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>580000000</v>
+        <v>209000000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-296000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>29000000</v>
-      </c>
+        <v>-329000000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>388000000</v>
+        <v>372000000</v>
       </c>
       <c r="AL2" t="n">
-        <v>121000000</v>
+        <v>43000000</v>
       </c>
       <c r="AM2" t="n">
-        <v>948000000</v>
+        <v>2288000000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1873000000</v>
+        <v>1433000000</v>
       </c>
       <c r="AO2" t="n">
-        <v>330000000</v>
+        <v>213000000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1543000000</v>
+        <v>1220000000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>848000000</v>
+        <v>617000000</v>
       </c>
       <c r="AR2" t="n">
-        <v>695000000</v>
+        <v>603000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2821000000</v>
+        <v>3721000000</v>
       </c>
       <c r="AT2" t="n">
-        <v>9261000000</v>
+        <v>8273000000</v>
       </c>
       <c r="AU2" t="n">
-        <v>12082000000</v>
+        <v>11994000000</v>
       </c>
       <c r="AV2" t="n">
-        <v>12082000000</v>
+        <v>11994000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-205600000</v>
+        <v>-62730000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="D3" t="n">
-        <v>1638000000</v>
+        <v>3415000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-514000000</v>
+        <v>-369000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-514000000</v>
+        <v>-369000000</v>
       </c>
       <c r="G3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
       <c r="H3" t="n">
-        <v>540000000</v>
+        <v>503000000</v>
       </c>
       <c r="I3" t="n">
-        <v>10445000000</v>
+        <v>10770000000</v>
       </c>
       <c r="J3" t="n">
-        <v>1124000000</v>
+        <v>3046000000</v>
       </c>
       <c r="K3" t="n">
-        <v>584000000</v>
+        <v>2543000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-312000000</v>
+        <v>-349000000</v>
       </c>
       <c r="M3" t="n">
-        <v>340000000</v>
+        <v>377000000</v>
       </c>
       <c r="N3" t="n">
-        <v>68000000</v>
+        <v>79000000</v>
       </c>
       <c r="O3" t="n">
-        <v>590400000</v>
+        <v>2099270000</v>
       </c>
       <c r="P3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>11971000000</v>
+        <v>12462000000</v>
       </c>
       <c r="R3" t="n">
-        <v>-79000000</v>
+        <v>1316000000</v>
       </c>
       <c r="S3" t="n">
         <v>15193014862</v>
@@ -858,140 +866,142 @@
         <v>15193014862</v>
       </c>
       <c r="U3" t="n">
-        <v>0.019</v>
+        <v>0.118</v>
       </c>
       <c r="V3" t="n">
-        <v>0.019</v>
+        <v>0.118</v>
       </c>
       <c r="W3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
       <c r="X3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-38000000</v>
+        <v>373000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>244000000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>2166000000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-163000000</v>
+      </c>
       <c r="AF3" t="n">
-        <v>-321000000</v>
+        <v>-196000000</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>321000000</v>
+        <v>196000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-312000000</v>
+        <v>-349000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>40000000</v>
+        <v>51000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>340000000</v>
+        <v>377000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>68000000</v>
+        <v>79000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>242000000</v>
+        <v>1512000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1526000000</v>
+        <v>1692000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>168000000</v>
+        <v>226000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1358000000</v>
+        <v>1466000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>755000000</v>
+        <v>697000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>603000000</v>
+        <v>769000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1768000000</v>
+        <v>3204000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>10445000000</v>
+        <v>10770000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>12213000000</v>
+        <v>13974000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>12213000000</v>
+        <v>13974000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-62730000</v>
+        <v>-205600000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3415000000</v>
+        <v>1638000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-369000000</v>
+        <v>-514000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-369000000</v>
+        <v>-514000000</v>
       </c>
       <c r="G4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
       <c r="H4" t="n">
-        <v>503000000</v>
+        <v>540000000</v>
       </c>
       <c r="I4" t="n">
-        <v>10770000000</v>
+        <v>10445000000</v>
       </c>
       <c r="J4" t="n">
-        <v>3046000000</v>
+        <v>1124000000</v>
       </c>
       <c r="K4" t="n">
-        <v>2543000000</v>
+        <v>584000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-349000000</v>
+        <v>-312000000</v>
       </c>
       <c r="M4" t="n">
-        <v>377000000</v>
+        <v>340000000</v>
       </c>
       <c r="N4" t="n">
-        <v>79000000</v>
+        <v>68000000</v>
       </c>
       <c r="O4" t="n">
-        <v>2099270000</v>
+        <v>590400000</v>
       </c>
       <c r="P4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>12462000000</v>
+        <v>11971000000</v>
       </c>
       <c r="R4" t="n">
-        <v>1316000000</v>
+        <v>-79000000</v>
       </c>
       <c r="S4" t="n">
         <v>15193014862</v>
@@ -1000,230 +1010,220 @@
         <v>15193014862</v>
       </c>
       <c r="U4" t="n">
-        <v>0.118</v>
+        <v>0.019</v>
       </c>
       <c r="V4" t="n">
-        <v>0.118</v>
+        <v>0.019</v>
       </c>
       <c r="W4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
       <c r="X4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>373000000</v>
+        <v>-38000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2166000000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-163000000</v>
-      </c>
+        <v>244000000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-196000000</v>
+        <v>-321000000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>196000000</v>
+        <v>321000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-349000000</v>
+        <v>-312000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>51000000</v>
+        <v>40000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>377000000</v>
+        <v>340000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>79000000</v>
+        <v>68000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1512000000</v>
+        <v>242000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1692000000</v>
+        <v>1526000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>226000000</v>
+        <v>168000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1466000000</v>
+        <v>1358000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>697000000</v>
+        <v>755000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>769000000</v>
+        <v>603000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3204000000</v>
+        <v>1768000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>10770000000</v>
+        <v>10445000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>13974000000</v>
+        <v>12213000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>13974000000</v>
+        <v>12213000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-12760000</v>
+        <v>-41089743.589744</v>
       </c>
       <c r="C5" t="n">
-        <v>0.11</v>
+        <v>0.06410299999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>4725000000</v>
+        <v>2425000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-116000000</v>
+        <v>-641000000</v>
       </c>
       <c r="F5" t="n">
-        <v>-116000000</v>
+        <v>-641000000</v>
       </c>
       <c r="G5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
       <c r="H5" t="n">
-        <v>596000000</v>
+        <v>538000000</v>
       </c>
       <c r="I5" t="n">
-        <v>8273000000</v>
+        <v>9261000000</v>
       </c>
       <c r="J5" t="n">
-        <v>4609000000</v>
+        <v>1784000000</v>
       </c>
       <c r="K5" t="n">
-        <v>4013000000</v>
+        <v>1246000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-329000000</v>
+        <v>-296000000</v>
       </c>
       <c r="M5" t="n">
-        <v>372000000</v>
+        <v>388000000</v>
       </c>
       <c r="N5" t="n">
-        <v>43000000</v>
+        <v>121000000</v>
       </c>
       <c r="O5" t="n">
-        <v>3328240000</v>
+        <v>1402910256.410256</v>
       </c>
       <c r="P5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>9706000000</v>
+        <v>11134000000</v>
       </c>
       <c r="R5" t="n">
-        <v>2079000000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>15193014862</v>
-      </c>
-      <c r="T5" t="n">
-        <v>15193014862</v>
-      </c>
+        <v>368000000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.212</v>
-      </c>
+        <v>0.053</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
       <c r="X5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>416000000</v>
+        <v>55000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3641000000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-60000000</v>
-      </c>
+        <v>858000000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>283000000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-492000000</v>
-      </c>
+        <v>-580000000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>209000000</v>
+        <v>580000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-329000000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-296000000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>29000000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>372000000</v>
+        <v>388000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>43000000</v>
+        <v>121000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2288000000</v>
+        <v>948000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1433000000</v>
+        <v>1873000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>213000000</v>
+        <v>330000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1220000000</v>
+        <v>1543000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>617000000</v>
+        <v>848000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>603000000</v>
+        <v>695000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3721000000</v>
+        <v>2821000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>8273000000</v>
+        <v>9261000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>11994000000</v>
+        <v>12082000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>11994000000</v>
+        <v>12082000000</v>
       </c>
     </row>
   </sheetData>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>15193014862</v>
@@ -1613,37 +1613,37 @@
         <v>15193014862</v>
       </c>
       <c r="D2" t="n">
-        <v>6417000000</v>
+        <v>4751000000</v>
       </c>
       <c r="E2" t="n">
-        <v>7918000000</v>
+        <v>6733000000</v>
       </c>
       <c r="F2" t="n">
-        <v>9015000000</v>
+        <v>8113000000</v>
       </c>
       <c r="G2" t="n">
-        <v>19134000000</v>
+        <v>17257000000</v>
       </c>
       <c r="H2" t="n">
-        <v>1602000000</v>
+        <v>3844000000</v>
       </c>
       <c r="I2" t="n">
-        <v>9015000000</v>
+        <v>8113000000</v>
       </c>
       <c r="J2" t="n">
-        <v>11216000000</v>
+        <v>10524000000</v>
       </c>
       <c r="K2" t="n">
-        <v>14614000000</v>
+        <v>15363000000</v>
       </c>
       <c r="L2" t="n">
-        <v>11216000000</v>
+        <v>10524000000</v>
       </c>
       <c r="M2" t="n">
-        <v>11216000000</v>
+        <v>10524000000</v>
       </c>
       <c r="N2" t="n">
-        <v>3627000000</v>
+        <v>1231000000</v>
       </c>
       <c r="O2" t="n">
         <v>15786000000</v>
@@ -1655,171 +1655,175 @@
         <v>152000000</v>
       </c>
       <c r="R2" t="n">
-        <v>10985000000</v>
+        <v>10382000000</v>
       </c>
       <c r="S2" t="n">
-        <v>4226000000</v>
+        <v>5790000000</v>
       </c>
       <c r="T2" t="n">
-        <v>119000000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>83000000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>61000000</v>
+      </c>
       <c r="V2" t="n">
-        <v>466000000</v>
+        <v>429000000</v>
       </c>
       <c r="W2" t="n">
-        <v>3398000000</v>
+        <v>4839000000</v>
       </c>
       <c r="X2" t="n">
-        <v>3398000000</v>
+        <v>4839000000</v>
       </c>
       <c r="Y2" t="n">
-        <v>243000000</v>
+        <v>378000000</v>
       </c>
       <c r="Z2" t="n">
-        <v>6759000000</v>
+        <v>4592000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>420000000</v>
+        <v>1116000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4520000000</v>
+        <v>1894000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>4520000000</v>
+        <v>1894000000</v>
       </c>
       <c r="AD2" t="n">
-        <v>96000000</v>
+        <v>145000000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1697000000</v>
+        <v>1292000000</v>
       </c>
       <c r="AF2" t="n">
-        <v>219000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>5000000</v>
-      </c>
+        <v>175000000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>195000000</v>
+        <v>221000000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1278000000</v>
+        <v>896000000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22201000000</v>
+        <v>20906000000</v>
       </c>
       <c r="AK2" t="n">
-        <v>13840000000</v>
+        <v>12470000000</v>
       </c>
       <c r="AL2" t="n">
-        <v>101000000</v>
+        <v>35000000</v>
       </c>
       <c r="AM2" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>315000000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>315000000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4014000000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2411000000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>142000000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2269000000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5350000000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-12159000000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17509000000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2618000000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3199000000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7142000000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4550000000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>8436000000</v>
+      </c>
+      <c r="BD2" t="n">
         <v>120000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>328000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>217000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>217000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4868000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2201000000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>187000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2014000000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6005000000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-11336000000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17341000000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2700000000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2083000000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7838000000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4720000000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8361000000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>19000000</v>
       </c>
       <c r="BE2" t="n">
         <v>2000000</v>
       </c>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BF2" t="n">
+        <v>691000000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>4477000000</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
+        <v>3692000000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-160000000</v>
+      </c>
       <c r="BI2" t="n">
-        <v>2182000000</v>
+        <v>1550000000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>848000000</v>
+        <v>779000000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1447000000</v>
+        <v>1363000000</v>
       </c>
       <c r="BL2" t="n">
-        <v>650000000</v>
+        <v>1002000000</v>
       </c>
       <c r="BM2" t="n">
-        <v>751000000</v>
+        <v>627000000</v>
       </c>
       <c r="BN2" t="n">
-        <v>849000000</v>
+        <v>844000000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-92000000</v>
+        <v>-18000000</v>
       </c>
       <c r="BP2" t="n">
-        <v>941000000</v>
+        <v>862000000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1613000000</v>
+        <v>2149000000</v>
       </c>
       <c r="BR2" t="n">
-        <v>112000000</v>
+        <v>167000000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1501000000</v>
+        <v>1982000000</v>
       </c>
       <c r="BT2" t="n">
-        <v>214000000</v>
+        <v>1109000000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1287000000</v>
+        <v>873000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>15193014862</v>
@@ -1828,37 +1832,37 @@
         <v>15193014862</v>
       </c>
       <c r="D3" t="n">
-        <v>5781000000</v>
+        <v>6264000000</v>
       </c>
       <c r="E3" t="n">
-        <v>7866000000</v>
+        <v>9457000000</v>
       </c>
       <c r="F3" t="n">
-        <v>8679000000</v>
+        <v>9702000000</v>
       </c>
       <c r="G3" t="n">
-        <v>18882000000</v>
+        <v>21764000000</v>
       </c>
       <c r="H3" t="n">
-        <v>4223000000</v>
+        <v>5524000000</v>
       </c>
       <c r="I3" t="n">
-        <v>8679000000</v>
+        <v>9702000000</v>
       </c>
       <c r="J3" t="n">
-        <v>11016000000</v>
+        <v>12307000000</v>
       </c>
       <c r="K3" t="n">
-        <v>16916000000</v>
+        <v>19217000000</v>
       </c>
       <c r="L3" t="n">
-        <v>11016000000</v>
+        <v>12307000000</v>
       </c>
       <c r="M3" t="n">
-        <v>11016000000</v>
+        <v>12307000000</v>
       </c>
       <c r="N3" t="n">
-        <v>3002000000</v>
+        <v>2720000000</v>
       </c>
       <c r="O3" t="n">
         <v>15786000000</v>
@@ -1870,171 +1874,175 @@
         <v>152000000</v>
       </c>
       <c r="R3" t="n">
-        <v>10448000000</v>
+        <v>12324000000</v>
       </c>
       <c r="S3" t="n">
-        <v>6729000000</v>
+        <v>7733000000</v>
       </c>
       <c r="T3" t="n">
-        <v>155000000</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>118000000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
       <c r="V3" t="n">
-        <v>405000000</v>
+        <v>427000000</v>
       </c>
       <c r="W3" t="n">
-        <v>5900000000</v>
+        <v>6910000000</v>
       </c>
       <c r="X3" t="n">
-        <v>5900000000</v>
+        <v>6910000000</v>
       </c>
       <c r="Y3" t="n">
-        <v>269000000</v>
+        <v>278000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>3719000000</v>
+        <v>4591000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>218000000</v>
+        <v>237000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1966000000</v>
+        <v>2547000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1966000000</v>
+        <v>2547000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>114000000</v>
+        <v>125000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1421000000</v>
+        <v>1682000000</v>
       </c>
       <c r="AF3" t="n">
-        <v>209000000</v>
+        <v>227000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>259000000</v>
+        <v>415000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>948000000</v>
+        <v>1040000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21464000000</v>
+        <v>24631000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>13522000000</v>
+        <v>14516000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>143000000</v>
+        <v>181000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>134000000</v>
+        <v>121000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>229000000</v>
+        <v>58000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>13000000</v>
+        <v>90000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>339000000</v>
+        <v>458000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>339000000</v>
+        <v>458000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>4521000000</v>
+        <v>5174000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2337000000</v>
+        <v>2605000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>181000000</v>
+        <v>171000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2156000000</v>
+        <v>2434000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>5806000000</v>
+        <v>5829000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-10708000000</v>
+        <v>-12794000000</v>
       </c>
       <c r="AX3" t="n">
-        <v>16514000000</v>
+        <v>18623000000</v>
       </c>
       <c r="AY3" t="n">
-        <v>3055000000</v>
+        <v>3047000000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1713000000</v>
+        <v>3489000000</v>
       </c>
       <c r="BA3" t="n">
-        <v>7398000000</v>
+        <v>7499000000</v>
       </c>
       <c r="BB3" t="n">
-        <v>4348000000</v>
+        <v>4588000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>7942000000</v>
+        <v>10115000000</v>
       </c>
       <c r="BD3" t="n">
-        <v>19000000</v>
+        <v>78000000</v>
       </c>
       <c r="BE3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>3000000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>812000000</v>
+      </c>
       <c r="BG3" t="n">
-        <v>3599000000</v>
+        <v>4489000000</v>
       </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>1500000000</v>
+        <v>2041000000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>766000000</v>
+        <v>906000000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1333000000</v>
+        <v>1542000000</v>
       </c>
       <c r="BL3" t="n">
-        <v>674000000</v>
+        <v>249000000</v>
       </c>
       <c r="BM3" t="n">
-        <v>546000000</v>
+        <v>977000000</v>
       </c>
       <c r="BN3" t="n">
-        <v>892000000</v>
+        <v>1037000000</v>
       </c>
       <c r="BO3" t="n">
-        <v>-68000000</v>
+        <v>-75000000</v>
       </c>
       <c r="BP3" t="n">
-        <v>960000000</v>
+        <v>1112000000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2210000000</v>
+        <v>3282000000</v>
       </c>
       <c r="BR3" t="n">
-        <v>125000000</v>
+        <v>89000000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2085000000</v>
+        <v>3193000000</v>
       </c>
       <c r="BT3" t="n">
-        <v>456000000</v>
+        <v>1461000000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1629000000</v>
+        <v>1732000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>15193014862</v>
@@ -2043,37 +2051,37 @@
         <v>15193014862</v>
       </c>
       <c r="D4" t="n">
-        <v>6264000000</v>
+        <v>5781000000</v>
       </c>
       <c r="E4" t="n">
-        <v>9457000000</v>
+        <v>7866000000</v>
       </c>
       <c r="F4" t="n">
-        <v>9702000000</v>
+        <v>8679000000</v>
       </c>
       <c r="G4" t="n">
-        <v>21764000000</v>
+        <v>18882000000</v>
       </c>
       <c r="H4" t="n">
-        <v>5524000000</v>
+        <v>4223000000</v>
       </c>
       <c r="I4" t="n">
-        <v>9702000000</v>
+        <v>8679000000</v>
       </c>
       <c r="J4" t="n">
-        <v>12307000000</v>
+        <v>11016000000</v>
       </c>
       <c r="K4" t="n">
-        <v>19217000000</v>
+        <v>16916000000</v>
       </c>
       <c r="L4" t="n">
-        <v>12307000000</v>
+        <v>11016000000</v>
       </c>
       <c r="M4" t="n">
-        <v>12307000000</v>
+        <v>11016000000</v>
       </c>
       <c r="N4" t="n">
-        <v>2720000000</v>
+        <v>3002000000</v>
       </c>
       <c r="O4" t="n">
         <v>15786000000</v>
@@ -2085,175 +2093,171 @@
         <v>152000000</v>
       </c>
       <c r="R4" t="n">
-        <v>12324000000</v>
+        <v>10448000000</v>
       </c>
       <c r="S4" t="n">
-        <v>7733000000</v>
+        <v>6729000000</v>
       </c>
       <c r="T4" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
+        <v>155000000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>427000000</v>
+        <v>405000000</v>
       </c>
       <c r="W4" t="n">
-        <v>6910000000</v>
+        <v>5900000000</v>
       </c>
       <c r="X4" t="n">
-        <v>6910000000</v>
+        <v>5900000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>278000000</v>
+        <v>269000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4591000000</v>
+        <v>3719000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>237000000</v>
+        <v>218000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2547000000</v>
+        <v>1966000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2547000000</v>
+        <v>1966000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>125000000</v>
+        <v>114000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1682000000</v>
+        <v>1421000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>227000000</v>
+        <v>209000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>415000000</v>
+        <v>259000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1040000000</v>
+        <v>948000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24631000000</v>
+        <v>21464000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>14516000000</v>
+        <v>13522000000</v>
       </c>
       <c r="AL4" t="n">
+        <v>143000000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>134000000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>339000000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>339000000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4521000000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2337000000</v>
+      </c>
+      <c r="AT4" t="n">
         <v>181000000</v>
       </c>
-      <c r="AM4" t="n">
-        <v>121000000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>458000000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>458000000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>5174000000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2605000000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>171000000</v>
-      </c>
       <c r="AU4" t="n">
-        <v>2434000000</v>
+        <v>2156000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>5829000000</v>
+        <v>5806000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-12794000000</v>
+        <v>-10708000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>18623000000</v>
+        <v>16514000000</v>
       </c>
       <c r="AY4" t="n">
-        <v>3047000000</v>
+        <v>3055000000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3489000000</v>
+        <v>1713000000</v>
       </c>
       <c r="BA4" t="n">
-        <v>7499000000</v>
+        <v>7398000000</v>
       </c>
       <c r="BB4" t="n">
-        <v>4588000000</v>
+        <v>4348000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>10115000000</v>
+        <v>7942000000</v>
       </c>
       <c r="BD4" t="n">
-        <v>78000000</v>
+        <v>19000000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>812000000</v>
-      </c>
+        <v>2000000</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>4489000000</v>
+        <v>3599000000</v>
       </c>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="n">
-        <v>2041000000</v>
+        <v>1500000000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>906000000</v>
+        <v>766000000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1542000000</v>
+        <v>1333000000</v>
       </c>
       <c r="BL4" t="n">
-        <v>249000000</v>
+        <v>674000000</v>
       </c>
       <c r="BM4" t="n">
-        <v>977000000</v>
+        <v>546000000</v>
       </c>
       <c r="BN4" t="n">
-        <v>1037000000</v>
+        <v>892000000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-75000000</v>
+        <v>-68000000</v>
       </c>
       <c r="BP4" t="n">
-        <v>1112000000</v>
+        <v>960000000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3282000000</v>
+        <v>2210000000</v>
       </c>
       <c r="BR4" t="n">
-        <v>89000000</v>
+        <v>125000000</v>
       </c>
       <c r="BS4" t="n">
-        <v>3193000000</v>
+        <v>2085000000</v>
       </c>
       <c r="BT4" t="n">
-        <v>1461000000</v>
+        <v>456000000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1732000000</v>
+        <v>1629000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>15193014862</v>
@@ -2262,37 +2266,37 @@
         <v>15193014862</v>
       </c>
       <c r="D5" t="n">
-        <v>4751000000</v>
+        <v>6417000000</v>
       </c>
       <c r="E5" t="n">
-        <v>6733000000</v>
+        <v>7918000000</v>
       </c>
       <c r="F5" t="n">
-        <v>8113000000</v>
+        <v>9015000000</v>
       </c>
       <c r="G5" t="n">
-        <v>17257000000</v>
+        <v>19134000000</v>
       </c>
       <c r="H5" t="n">
-        <v>3844000000</v>
+        <v>1602000000</v>
       </c>
       <c r="I5" t="n">
-        <v>8113000000</v>
+        <v>9015000000</v>
       </c>
       <c r="J5" t="n">
-        <v>10524000000</v>
+        <v>11216000000</v>
       </c>
       <c r="K5" t="n">
-        <v>15363000000</v>
+        <v>14614000000</v>
       </c>
       <c r="L5" t="n">
-        <v>10524000000</v>
+        <v>11216000000</v>
       </c>
       <c r="M5" t="n">
-        <v>10524000000</v>
+        <v>11216000000</v>
       </c>
       <c r="N5" t="n">
-        <v>1231000000</v>
+        <v>3627000000</v>
       </c>
       <c r="O5" t="n">
         <v>15786000000</v>
@@ -2304,170 +2308,166 @@
         <v>152000000</v>
       </c>
       <c r="R5" t="n">
-        <v>10382000000</v>
+        <v>10985000000</v>
       </c>
       <c r="S5" t="n">
-        <v>5790000000</v>
+        <v>4226000000</v>
       </c>
       <c r="T5" t="n">
-        <v>83000000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>61000000</v>
-      </c>
+        <v>119000000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>429000000</v>
+        <v>466000000</v>
       </c>
       <c r="W5" t="n">
-        <v>4839000000</v>
+        <v>3398000000</v>
       </c>
       <c r="X5" t="n">
-        <v>4839000000</v>
+        <v>3398000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>378000000</v>
+        <v>243000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>4592000000</v>
+        <v>6759000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1116000000</v>
+        <v>420000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1894000000</v>
+        <v>4520000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1894000000</v>
+        <v>4520000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>145000000</v>
+        <v>96000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1292000000</v>
+        <v>1697000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>175000000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>219000000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5000000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>221000000</v>
+        <v>195000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>896000000</v>
+        <v>1278000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20906000000</v>
+        <v>22201000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>12470000000</v>
+        <v>13840000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>35000000</v>
+        <v>101000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>210000000</v>
+        <v>120000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>113000000</v>
+        <v>328000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>22000000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>315000000</v>
+        <v>217000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>315000000</v>
+        <v>217000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>4014000000</v>
+        <v>4868000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2411000000</v>
+        <v>2201000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>142000000</v>
+        <v>187000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2269000000</v>
+        <v>2014000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>5350000000</v>
+        <v>6005000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-12159000000</v>
+        <v>-11336000000</v>
       </c>
       <c r="AX5" t="n">
-        <v>17509000000</v>
+        <v>17341000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2618000000</v>
+        <v>2700000000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3199000000</v>
+        <v>2083000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>7142000000</v>
+        <v>7838000000</v>
       </c>
       <c r="BB5" t="n">
-        <v>4550000000</v>
+        <v>4720000000</v>
       </c>
       <c r="BC5" t="n">
-        <v>8436000000</v>
+        <v>8361000000</v>
       </c>
       <c r="BD5" t="n">
-        <v>120000000</v>
+        <v>19000000</v>
       </c>
       <c r="BE5" t="n">
         <v>2000000</v>
       </c>
-      <c r="BF5" t="n">
-        <v>691000000</v>
-      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>3692000000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>-160000000</v>
-      </c>
+        <v>4477000000</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>1550000000</v>
+        <v>2182000000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>779000000</v>
+        <v>848000000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1363000000</v>
+        <v>1447000000</v>
       </c>
       <c r="BL5" t="n">
-        <v>1002000000</v>
+        <v>650000000</v>
       </c>
       <c r="BM5" t="n">
-        <v>627000000</v>
+        <v>751000000</v>
       </c>
       <c r="BN5" t="n">
-        <v>844000000</v>
+        <v>849000000</v>
       </c>
       <c r="BO5" t="n">
-        <v>-18000000</v>
+        <v>-92000000</v>
       </c>
       <c r="BP5" t="n">
-        <v>862000000</v>
+        <v>941000000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2149000000</v>
+        <v>1613000000</v>
       </c>
       <c r="BR5" t="n">
-        <v>167000000</v>
+        <v>112000000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1982000000</v>
+        <v>1501000000</v>
       </c>
       <c r="BT5" t="n">
-        <v>1109000000</v>
+        <v>214000000</v>
       </c>
       <c r="BU5" t="n">
-        <v>873000000</v>
+        <v>1287000000</v>
       </c>
     </row>
   </sheetData>
@@ -2743,608 +2743,608 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-883000000</v>
+        <v>-46000000</v>
       </c>
       <c r="C2" t="n">
-        <v>-2069000000</v>
+        <v>-2080000000</v>
       </c>
       <c r="D2" t="n">
-        <v>2628000000</v>
+        <v>918000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1366000000</v>
+        <v>-1192000000</v>
       </c>
       <c r="F2" t="n">
-        <v>1501000000</v>
+        <v>1982000000</v>
       </c>
       <c r="G2" t="n">
-        <v>2085000000</v>
+        <v>2216000000</v>
       </c>
       <c r="H2" t="n">
-        <v>-102000000</v>
+        <v>21000000</v>
       </c>
       <c r="I2" t="n">
-        <v>-482000000</v>
+        <v>-255000000</v>
       </c>
       <c r="J2" t="n">
-        <v>113000000</v>
+        <v>-1891000000</v>
       </c>
       <c r="K2" t="n">
-        <v>63000000</v>
+        <v>-315000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-494000000</v>
+        <v>-380000000</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>559000000</v>
+        <v>-1162000000</v>
       </c>
       <c r="P2" t="n">
-        <v>559000000</v>
+        <v>-1162000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2069000000</v>
+        <v>-2080000000</v>
       </c>
       <c r="R2" t="n">
-        <v>2628000000</v>
+        <v>918000000</v>
       </c>
       <c r="S2" t="n">
-        <v>-1078000000</v>
+        <v>490000000</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>116000000</v>
+        <v>37000000</v>
       </c>
       <c r="V2" t="n">
+        <v>640000000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-341000000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>-341000000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1336000000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1421000000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-85000000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-28000000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-28000000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1154000000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1164000000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1146000000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-307000000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-1537000000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>394000000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-1387000000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-528000000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>335000000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>416000000</v>
       </c>
-      <c r="W2" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-303000000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-303000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-34000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-34000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1318000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1332000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>483000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-127000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-923000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>474000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-841000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-551000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>292000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-3000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>55000000</v>
-      </c>
       <c r="AR2" t="n">
-        <v>538000000</v>
+        <v>596000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>26000000</v>
+        <v>7000000</v>
       </c>
       <c r="AT2" t="n">
-        <v>512000000</v>
+        <v>589000000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="AV2" t="n">
-        <v>61000000</v>
+        <v>379000000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-283000000</v>
+        <v>29000000</v>
       </c>
       <c r="AX2" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>9000000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-492000000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>803000000</v>
+        <v>3225000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>704000000</v>
+        <v>-1651000000</v>
       </c>
       <c r="C3" t="n">
-        <v>-4814000000</v>
+        <v>-3645000000</v>
       </c>
       <c r="D3" t="n">
-        <v>3521000000</v>
+        <v>6036000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-1056000000</v>
+        <v>-1239000000</v>
       </c>
       <c r="F3" t="n">
-        <v>2085000000</v>
+        <v>3193000000</v>
       </c>
       <c r="G3" t="n">
-        <v>3193000000</v>
+        <v>1982000000</v>
       </c>
       <c r="H3" t="n">
-        <v>-91000000</v>
+        <v>-264000000</v>
       </c>
       <c r="I3" t="n">
-        <v>-1017000000</v>
+        <v>1475000000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1747000000</v>
+        <v>1415000000</v>
       </c>
       <c r="K3" t="n">
-        <v>-2000000</v>
+        <v>-229000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-422000000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>-428000000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-302000000</v>
+      </c>
       <c r="N3" t="n">
+        <v>-302000000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2391000000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2391000000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-3645000000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6036000000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>472000000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1671000000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-113000000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>97000000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-113000000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="AA3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>-1293000000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1293000000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-4814000000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3521000000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-1030000000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>61000000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-54000000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>-54000000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-13000000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-13000000</v>
+        <v>-16000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-34000000</v>
+        <v>-37000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-34000000</v>
+        <v>-37000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1012000000</v>
+        <v>-1199000000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10000000</v>
+        <v>3000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1022000000</v>
+        <v>-1202000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1760000000</v>
+        <v>-412000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-125000000</v>
+        <v>-358000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1104000000</v>
+        <v>-2422000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-208000000</v>
+        <v>-846000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>923000000</v>
+        <v>-1245000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>393000000</v>
+        <v>-325000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>314000000</v>
+        <v>351000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-12000000</v>
+        <v>171000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-38000000</v>
+        <v>373000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>540000000</v>
+        <v>503000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>19000000</v>
+        <v>12000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>521000000</v>
+        <v>491000000</v>
       </c>
       <c r="AU3" t="n">
         <v>4000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>168000000</v>
+        <v>137000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-51000000</v>
+        <v>219000000</v>
       </c>
       <c r="AX3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>13000000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>282000000</v>
+        <v>1793000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1651000000</v>
+        <v>704000000</v>
       </c>
       <c r="C4" t="n">
-        <v>-3645000000</v>
+        <v>-4814000000</v>
       </c>
       <c r="D4" t="n">
-        <v>6036000000</v>
+        <v>3521000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1239000000</v>
+        <v>-1056000000</v>
       </c>
       <c r="F4" t="n">
+        <v>2085000000</v>
+      </c>
+      <c r="G4" t="n">
         <v>3193000000</v>
       </c>
-      <c r="G4" t="n">
-        <v>1982000000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-264000000</v>
+        <v>-91000000</v>
       </c>
       <c r="I4" t="n">
-        <v>1475000000</v>
+        <v>-1017000000</v>
       </c>
       <c r="J4" t="n">
-        <v>1415000000</v>
+        <v>-1747000000</v>
       </c>
       <c r="K4" t="n">
-        <v>-229000000</v>
+        <v>-2000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-428000000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-302000000</v>
-      </c>
+        <v>-422000000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-302000000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2391000000</v>
+        <v>-1293000000</v>
       </c>
       <c r="P4" t="n">
-        <v>2391000000</v>
+        <v>-1293000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3645000000</v>
+        <v>-4814000000</v>
       </c>
       <c r="R4" t="n">
-        <v>6036000000</v>
+        <v>3521000000</v>
       </c>
       <c r="S4" t="n">
-        <v>472000000</v>
+        <v>-1030000000</v>
       </c>
       <c r="T4" t="n">
-        <v>96000000</v>
+        <v>1000000</v>
       </c>
       <c r="U4" t="n">
-        <v>70000000</v>
+        <v>61000000</v>
       </c>
       <c r="V4" t="n">
-        <v>1671000000</v>
+        <v>21000000</v>
       </c>
       <c r="W4" t="n">
-        <v>-113000000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>97000000</v>
-      </c>
+        <v>-54000000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-113000000</v>
+        <v>-54000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-16000000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>-13000000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-16000000</v>
+        <v>-13000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-37000000</v>
+        <v>-34000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-37000000</v>
+        <v>-34000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1199000000</v>
+        <v>-1012000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1202000000</v>
+        <v>-1022000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-412000000</v>
+        <v>1760000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-358000000</v>
+        <v>-125000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2422000000</v>
+        <v>1104000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>4000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-846000000</v>
+        <v>-208000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1245000000</v>
+        <v>923000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-325000000</v>
+        <v>393000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>351000000</v>
+        <v>314000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>171000000</v>
+        <v>-12000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>373000000</v>
+        <v>-38000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>503000000</v>
+        <v>540000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>12000000</v>
+        <v>19000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>491000000</v>
+        <v>521000000</v>
       </c>
       <c r="AU4" t="n">
         <v>4000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>137000000</v>
+        <v>168000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>219000000</v>
+        <v>-51000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
+        <v>4000000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>1793000000</v>
+        <v>282000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-46000000</v>
+        <v>-883000000</v>
       </c>
       <c r="C5" t="n">
-        <v>-2080000000</v>
+        <v>-2069000000</v>
       </c>
       <c r="D5" t="n">
-        <v>918000000</v>
+        <v>2628000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1192000000</v>
+        <v>-1366000000</v>
       </c>
       <c r="F5" t="n">
-        <v>1982000000</v>
+        <v>1501000000</v>
       </c>
       <c r="G5" t="n">
-        <v>2216000000</v>
+        <v>2085000000</v>
       </c>
       <c r="H5" t="n">
-        <v>21000000</v>
+        <v>-102000000</v>
       </c>
       <c r="I5" t="n">
-        <v>-255000000</v>
+        <v>-482000000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1891000000</v>
+        <v>113000000</v>
       </c>
       <c r="K5" t="n">
-        <v>-315000000</v>
+        <v>63000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-380000000</v>
+        <v>-494000000</v>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-1162000000</v>
+        <v>559000000</v>
       </c>
       <c r="P5" t="n">
-        <v>-1162000000</v>
+        <v>559000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2080000000</v>
+        <v>-2069000000</v>
       </c>
       <c r="R5" t="n">
-        <v>918000000</v>
+        <v>2628000000</v>
       </c>
       <c r="S5" t="n">
-        <v>490000000</v>
+        <v>-1078000000</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>37000000</v>
+        <v>116000000</v>
       </c>
       <c r="V5" t="n">
-        <v>640000000</v>
+        <v>416000000</v>
       </c>
       <c r="W5" t="n">
-        <v>-341000000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>45000000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>45000000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>-341000000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1336000000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1421000000</v>
-      </c>
+        <v>-303000000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-85000000</v>
+        <v>-303000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-28000000</v>
+        <v>-34000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-28000000</v>
+        <v>-34000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1154000000</v>
+        <v>-1318000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10000000</v>
+        <v>14000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1164000000</v>
+        <v>-1332000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1146000000</v>
+        <v>483000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-307000000</v>
+        <v>-127000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1537000000</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>-923000000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
       <c r="AL5" t="n">
-        <v>394000000</v>
+        <v>474000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1387000000</v>
+        <v>-841000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-528000000</v>
+        <v>-551000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>335000000</v>
+        <v>292000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6000000</v>
+        <v>-3000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>416000000</v>
+        <v>55000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>596000000</v>
+        <v>538000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>7000000</v>
+        <v>26000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>589000000</v>
+        <v>512000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>379000000</v>
+        <v>61000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>29000000</v>
+        <v>-283000000</v>
       </c>
       <c r="AX5" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-492000000</v>
-      </c>
+        <v>8000000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>3225000000</v>
+        <v>803000000</v>
       </c>
     </row>
   </sheetData>
@@ -3894,202 +3894,202 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EQ1" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Evgenii Viktorovich Nikitin', 'age': 59, 'title': 'General Director &amp; Executive Director', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 21864004, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Natalia  Albrekht', 'age': 53, 'title': 'Executive Director &amp; Deputy General Director-HR', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 15289130, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ivanova Elena Anatolievna', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 1528129, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Victor  Mann', 'age': 67, 'title': 'Technical Director', 'yearBorn': 1958, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Alexander  Pakhomov', 'age': 52, 'title': 'Head of Compliance', 'yearBorn': 1973, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yakov  Itskov', 'age': 59, 'title': 'Head of Alumina Division', 'yearBorn': 1966, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Evgeny  Zenkin', 'title': 'Managing Director of The Bratsk Aluminium Smelter', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Oleg  Buts', 'title': 'Managing Director of Irkutsk Aluminium Smelter', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Aleksey  Gordymov', 'age': 53, 'title': 'Head of Supply Chain', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Denis  Nushtaev', 'age': 49, 'title': 'Head of Research Department', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Evgenii Viktorovich Nikitin', 'age': 59, 'title': 'General Director &amp; Executive Director', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 21865546, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Natalia  Albrekht', 'age': 53, 'title': 'Executive Director &amp; Deputy General Director-HR', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 15290208, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ivanova Elena Anatolievna', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 1528237, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Victor  Mann', 'age': 67, 'title': 'Technical Director', 'yearBorn': 1958, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Alexander  Pakhomov', 'age': 52, 'title': 'Head of Compliance', 'yearBorn': 1973, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yakov  Itskov', 'age': 59, 'title': 'Head of Alumina Division', 'yearBorn': 1966, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Evgeny  Zenkin', 'title': 'Managing Director of The Bratsk Aluminium Smelter', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Oleg  Buts', 'title': 'Managing Director of Irkutsk Aluminium Smelter', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Aleksey  Gordymov', 'age': 53, 'title': 'Head of Supply Chain', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Denis  Nushtaev', 'age': 49, 'title': 'Head of Research Department', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4197,28 +4197,28 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="X2" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="AD2" t="n">
         <v>1666137600</v>
@@ -4227,31 +4227,31 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.666</v>
+        <v>0.621</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3874998</v>
+        <v>2.0625</v>
       </c>
       <c r="AH2" t="n">
-        <v>688000</v>
+        <v>452147</v>
       </c>
       <c r="AI2" t="n">
-        <v>688000</v>
+        <v>452147</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1279913</v>
+        <v>696056</v>
       </c>
       <c r="AK2" t="n">
-        <v>715092</v>
+        <v>451350</v>
       </c>
       <c r="AL2" t="n">
-        <v>715092</v>
+        <v>451350</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.79</v>
+        <v>3.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.82</v>
+        <v>3.37</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -4260,13 +4260,13 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>58037317632</v>
+        <v>50136948736</v>
       </c>
       <c r="AR2" t="n">
-        <v>53175552017</v>
+        <v>51352390233</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.49</v>
+        <v>3.21</v>
       </c>
       <c r="AT2" t="n">
         <v>7</v>
@@ -4278,13 +4278,13 @@
         <v>1.31</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.9182634</v>
+        <v>3.3848872</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.137</v>
+        <v>4.0116</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.61235</v>
+        <v>4.566</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>66044317696</v>
+        <v>58143948800</v>
       </c>
       <c r="BE2" t="n">
         <v>-0.030720001</v>
@@ -4313,19 +4313,19 @@
         <v>15193014862</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.79842</v>
+        <v>0.79689</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0103400005</v>
+        <v>0.009990000000000001</v>
       </c>
       <c r="BJ2" t="n">
         <v>15193014862</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.0498247</v>
+        <v>6.050299</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.63142323</v>
+        <v>0.54542756</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4340,7 +4340,7 @@
         <v>-455000000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="BR2" t="n">
         <v>1.6</v>
@@ -4349,16 +4349,16 @@
         <v>0.23</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.459</v>
+        <v>3.925</v>
       </c>
       <c r="BU2" t="n">
-        <v>63.443</v>
+        <v>55.854</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.09560722000000001</v>
+        <v>-0.12207794</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.02</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4471,153 +4471,153 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DC2" t="n">
+        <v>-0.08000016</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>3.21 - 3.38</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>RUSAL</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>United Company RUSAL, International Public Joint-Stock Company</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>9.142856</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="DH2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>finmb_8101878</t>
-        </is>
+        <v>696056</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.089999914</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.028037356</v>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
+          <t>3.21 - 7.0</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>-3.7</v>
       </c>
       <c r="DM2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>-0.5285714</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-12.207794</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1747220340</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1747220340</v>
       </c>
       <c r="DQ2" t="b">
         <v>0</v>
       </c>
       <c r="DR2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.71160007</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.1773856</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-1.266</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.27726677</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>United Company RUSAL Plc</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1782115164</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-2.3668685</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>finmb_8101878</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EL2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EP2" t="n">
         <v>1264555800000</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.31999993</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>3.5 - 3.85</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>1279913</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.32999992</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.09455585499999999</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>3.49 - 7.0</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.4542857</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-9.560722</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1747220340</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1747220340</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.31700015</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.07662561</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-0.79235005</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.1717888</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>United Company RUSAL Plc</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EP2" t="b">
-        <v>0</v>
       </c>
       <c r="EQ2" t="inlineStr"/>
     </row>
